--- a/Hardware/Buck Converter.xlsx
+++ b/Hardware/Buck Converter.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\angel\Desktop\Proyectos\FOC BLDC\Hardware\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\angel\Desktop\Proyectos\FOC_BLDC\Hardware\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{20B1B338-48D6-4EEC-88C4-B1FD0F68876F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F4E28D9-E4B3-4C44-B6B7-357A5D3A4116}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="14616" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="45">
   <si>
     <t>Data</t>
   </si>
@@ -192,14 +192,23 @@
   <si>
     <t>Limit to 40A</t>
   </si>
+  <si>
+    <t>Second pole</t>
+  </si>
+  <si>
+    <t>Power stage pole</t>
+  </si>
+  <si>
+    <t>loop BW</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
-    <numFmt numFmtId="165" formatCode="0.00000"/>
-    <numFmt numFmtId="166" formatCode="0.0000"/>
+    <numFmt numFmtId="164" formatCode="0.00000"/>
+    <numFmt numFmtId="165" formatCode="0.0000"/>
   </numFmts>
   <fonts count="2" x14ac:knownFonts="1">
     <font>
@@ -291,17 +300,17 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="11" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -604,11 +613,11 @@
       <c r="C1" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="E1" s="13" t="s">
+      <c r="E1" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="F1" s="13"/>
-      <c r="G1" s="14" t="s">
+      <c r="F1" s="14"/>
+      <c r="G1" s="13" t="s">
         <v>31</v>
       </c>
     </row>
@@ -785,7 +794,9 @@
       <c r="B11" s="1">
         <v>50</v>
       </c>
-      <c r="C11" s="4"/>
+      <c r="C11" s="4" t="s">
+        <v>44</v>
+      </c>
       <c r="E11" s="1" t="s">
         <v>23</v>
       </c>
@@ -804,6 +815,9 @@
         <v>974.41801892997148</v>
       </c>
       <c r="G12" s="1"/>
+      <c r="H12" t="s">
+        <v>43</v>
+      </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.3">
       <c r="E13" s="1" t="s">
@@ -814,6 +828,9 @@
         <v>292.5</v>
       </c>
       <c r="G13" s="1"/>
+      <c r="H13" t="s">
+        <v>42</v>
+      </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.3">
       <c r="E14" s="1" t="s">

--- a/Hardware/Buck Converter.xlsx
+++ b/Hardware/Buck Converter.xlsx
@@ -1,19 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\angel\Desktop\Proyectos\FOC_BLDC\Hardware\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F4E28D9-E4B3-4C44-B6B7-357A5D3A4116}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90614B28-8C13-4814-AF35-C3A61FF40A89}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="14616" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="16 to 5" sheetId="2" r:id="rId1"/>
+    <sheet name="36 to 16" sheetId="3" r:id="rId2"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -35,8 +37,130 @@
 </workbook>
 </file>
 
+<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata">
+  <metadataTypes count="1">
+    <metadataType name="XLRICHVALUE" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1"/>
+  </metadataTypes>
+  <futureMetadata name="XLRICHVALUE" count="11">
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="0"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="1"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="2"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="3"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="4"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="5"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="6"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="7"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="8"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="9"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="10"/>
+        </ext>
+      </extLst>
+    </bk>
+  </futureMetadata>
+  <valueMetadata count="11">
+    <bk>
+      <rc t="1" v="0"/>
+    </bk>
+    <bk>
+      <rc t="1" v="1"/>
+    </bk>
+    <bk>
+      <rc t="1" v="2"/>
+    </bk>
+    <bk>
+      <rc t="1" v="3"/>
+    </bk>
+    <bk>
+      <rc t="1" v="4"/>
+    </bk>
+    <bk>
+      <rc t="1" v="5"/>
+    </bk>
+    <bk>
+      <rc t="1" v="6"/>
+    </bk>
+    <bk>
+      <rc t="1" v="7"/>
+    </bk>
+    <bk>
+      <rc t="1" v="8"/>
+    </bk>
+    <bk>
+      <rc t="1" v="9"/>
+    </bk>
+    <bk>
+      <rc t="1" v="10"/>
+    </bk>
+  </valueMetadata>
+</metadata>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="78">
   <si>
     <t>Data</t>
   </si>
@@ -201,6 +325,127 @@
   <si>
     <t>loop BW</t>
   </si>
+  <si>
+    <t>Max voltage ripple (mV)</t>
+  </si>
+  <si>
+    <t>100 - 2500, the higher more heat</t>
+  </si>
+  <si>
+    <t>Pin RT_CLK pull down</t>
+  </si>
+  <si>
+    <t>Kind</t>
+  </si>
+  <si>
+    <t>% over max current for ind</t>
+  </si>
+  <si>
+    <t>Max Output Current (mA)</t>
+  </si>
+  <si>
+    <t>Max current rating 100% + Kind of max output</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Lo </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>min</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Inductance (H)</t>
+    </r>
+  </si>
+  <si>
+    <t>Choose largest between both</t>
+  </si>
+  <si>
+    <t>Modify R2 to obtain a proper value for R1</t>
+  </si>
+  <si>
+    <t>Value for Vsense and obtain correct Vout</t>
+  </si>
+  <si>
+    <t>Reverse voltage max diode</t>
+  </si>
+  <si>
+    <t>Must be greater than Vin</t>
+  </si>
+  <si>
+    <t>60 V</t>
+  </si>
+  <si>
+    <t>Current greater than max out currrent</t>
+  </si>
+  <si>
+    <t>B360</t>
+  </si>
+  <si>
+    <t>gm(ps) (A/V)</t>
+  </si>
+  <si>
+    <t>For this chip</t>
+  </si>
+  <si>
+    <t>Ro (Ω) = Rload</t>
+  </si>
+  <si>
+    <t>R3 (kΩ) = Rc</t>
+  </si>
+  <si>
+    <t>Gmod(fc)</t>
+  </si>
+  <si>
+    <t>gm(EA) (uA/V)</t>
+  </si>
+  <si>
+    <t>fc</t>
+  </si>
+  <si>
+    <t>Sw freq / 10</t>
+  </si>
+  <si>
+    <t>fp (Hz)</t>
+  </si>
+  <si>
+    <t>Using ripple current, variation of Iout to 50% of max range</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50 mV for Vout 5V </t>
+  </si>
+  <si>
+    <t>160mV for 16V</t>
+  </si>
+  <si>
+    <t>0402</t>
+  </si>
+  <si>
+    <t>1nF</t>
+  </si>
+  <si>
+    <t>% over max current for ind, decrease for lower ripple</t>
+  </si>
+  <si>
+    <t>C2 (pF) = Cc (Series)</t>
+  </si>
+  <si>
+    <t>C1 (pF) = Cf (Parallel)</t>
+  </si>
 </sst>
 </file>
 
@@ -210,7 +455,7 @@
     <numFmt numFmtId="164" formatCode="0.00000"/>
     <numFmt numFmtId="165" formatCode="0.0000"/>
   </numFmts>
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -224,8 +469,22 @@
       <name val="Aptos Narrow"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -250,8 +509,20 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="3">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -287,11 +558,20 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="43">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
@@ -310,6 +590,90 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="11" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -326,6 +690,120 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/richData/rdRichValueTypes.xml><?xml version="1.0" encoding="utf-8"?>
+<rvTypesInfo xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x">
+  <global>
+    <keyFlags>
+      <key name="_Self">
+        <flag name="ExcludeFromFile" value="1"/>
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_DisplayString">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_Flags">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_Format">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_SubLabel">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_Attribution">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_Icon">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_Display">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_CanonicalPropertyNames">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_ClassificationId">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+    </keyFlags>
+  </global>
+</rvTypesInfo>
+</file>
+
+<file path=xl/richData/rdrichvalue.xml><?xml version="1.0" encoding="utf-8"?>
+<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="11">
+  <rv s="0">
+    <v>0</v>
+    <v>5</v>
+  </rv>
+  <rv s="0">
+    <v>1</v>
+    <v>5</v>
+  </rv>
+  <rv s="0">
+    <v>2</v>
+    <v>5</v>
+  </rv>
+  <rv s="0">
+    <v>3</v>
+    <v>5</v>
+  </rv>
+  <rv s="0">
+    <v>4</v>
+    <v>5</v>
+  </rv>
+  <rv s="0">
+    <v>5</v>
+    <v>5</v>
+  </rv>
+  <rv s="0">
+    <v>6</v>
+    <v>5</v>
+  </rv>
+  <rv s="0">
+    <v>7</v>
+    <v>5</v>
+  </rv>
+  <rv s="0">
+    <v>8</v>
+    <v>5</v>
+  </rv>
+  <rv s="0">
+    <v>9</v>
+    <v>5</v>
+  </rv>
+  <rv s="0">
+    <v>10</v>
+    <v>5</v>
+  </rv>
+</rvData>
+</file>
+
+<file path=xl/richData/rdrichvaluestructure.xml><?xml version="1.0" encoding="utf-8"?>
+<rvStructures xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="1">
+  <s t="_localImage">
+    <k n="_rvRel:LocalImageIdentifier" t="i"/>
+    <k n="CalcOrigin" t="i"/>
+  </s>
+</rvStructures>
+</file>
+
+<file path=xl/richData/richValueRel.xml><?xml version="1.0" encoding="utf-8"?>
+<richValueRels xmlns="http://schemas.microsoft.com/office/spreadsheetml/2022/richvaluerel" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <rel r:id="rId1"/>
+  <rel r:id="rId2"/>
+  <rel r:id="rId3"/>
+  <rel r:id="rId4"/>
+  <rel r:id="rId5"/>
+  <rel r:id="rId6"/>
+  <rel r:id="rId7"/>
+  <rel r:id="rId8"/>
+  <rel r:id="rId9"/>
+  <rel r:id="rId10"/>
+  <rel r:id="rId11"/>
+</richValueRels>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -590,8 +1068,904 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0E861262-2E2E-438C-9044-040EB1C596A1}">
+  <dimension ref="A1:M25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="24.5546875" style="16" customWidth="1"/>
+    <col min="2" max="2" width="9.88671875" style="16" customWidth="1"/>
+    <col min="3" max="3" width="22.5546875" style="16" customWidth="1"/>
+    <col min="4" max="4" width="8.88671875" style="16"/>
+    <col min="5" max="5" width="23.77734375" style="16" customWidth="1"/>
+    <col min="6" max="6" width="8.44140625" style="29" customWidth="1"/>
+    <col min="7" max="7" width="11.21875" style="16" customWidth="1"/>
+    <col min="8" max="8" width="12" style="16" customWidth="1"/>
+    <col min="9" max="12" width="8.88671875" style="16"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A1" s="15" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="15" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1" s="17" t="s">
+        <v>7</v>
+      </c>
+      <c r="F1" s="17"/>
+      <c r="G1" s="18" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" ht="43.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="19" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="34">
+        <v>16</v>
+      </c>
+      <c r="C2" s="33"/>
+      <c r="E2" s="22" t="s">
+        <v>3</v>
+      </c>
+      <c r="F2" s="38">
+        <f>206033/(B4^1.0888)</f>
+        <v>200.01265706102132</v>
+      </c>
+      <c r="G2" s="20"/>
+      <c r="H2" s="31" t="e" vm="1">
+        <v>#VALUE!</v>
+      </c>
+      <c r="I2" s="30"/>
+      <c r="J2" s="30"/>
+      <c r="K2" s="16" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" ht="37.200000000000003" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="19" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" s="34">
+        <v>5</v>
+      </c>
+      <c r="C3" s="33"/>
+      <c r="E3" s="20" t="s">
+        <v>52</v>
+      </c>
+      <c r="F3" s="25">
+        <f xml:space="preserve"> ((B2-B3)/(B5*B10))*(B3/(B2*B4))</f>
+        <v>1.3057929724596393E-5</v>
+      </c>
+      <c r="G3" s="39">
+        <f>12*10^-6</f>
+        <v>1.2E-5</v>
+      </c>
+      <c r="H3" s="31" t="e" vm="2">
+        <v>#VALUE!</v>
+      </c>
+      <c r="I3" s="36"/>
+      <c r="J3" s="36"/>
+      <c r="K3" s="36"/>
+      <c r="L3" s="16" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" ht="40.799999999999997" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="19" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4" s="34">
+        <v>585</v>
+      </c>
+      <c r="C4" s="32" t="s">
+        <v>46</v>
+      </c>
+      <c r="E4" s="20" t="s">
+        <v>10</v>
+      </c>
+      <c r="F4" s="24">
+        <f>F5*(B3-0.8)/0.8</f>
+        <v>52.5</v>
+      </c>
+      <c r="G4" s="39">
+        <v>52.3</v>
+      </c>
+      <c r="H4" s="31" t="e" vm="3">
+        <v>#VALUE!</v>
+      </c>
+      <c r="I4" s="36"/>
+      <c r="J4" s="36"/>
+      <c r="K4" s="16" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" ht="27.6" x14ac:dyDescent="0.3">
+      <c r="A5" s="19" t="s">
+        <v>48</v>
+      </c>
+      <c r="B5" s="33">
+        <v>0.3</v>
+      </c>
+      <c r="C5" s="32" t="s">
+        <v>75</v>
+      </c>
+      <c r="E5" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="F5" s="40">
+        <v>10</v>
+      </c>
+      <c r="G5" s="20"/>
+      <c r="H5" s="16" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A6" s="19" t="s">
+        <v>12</v>
+      </c>
+      <c r="B6" s="33">
+        <v>0.8</v>
+      </c>
+      <c r="C6" s="33"/>
+      <c r="E6" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="F6" s="24">
+        <f>(B8*B7)/(B6*0.8)</f>
+        <v>15.624999999999996</v>
+      </c>
+      <c r="G6" s="20"/>
+    </row>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A7" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="B7" s="33">
+        <v>2</v>
+      </c>
+      <c r="C7" s="33"/>
+      <c r="E7" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="F7" s="24">
+        <f>B3/(B2*B9)</f>
+        <v>0.36764705882352944</v>
+      </c>
+      <c r="G7" s="20"/>
+    </row>
+    <row r="8" spans="1:13" ht="40.200000000000003" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="19" t="s">
+        <v>14</v>
+      </c>
+      <c r="B8" s="33">
+        <v>5</v>
+      </c>
+      <c r="C8" s="33"/>
+      <c r="E8" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="F8" s="24">
+        <f>(B3*(B2-B3))/(B2*G3*B4)</f>
+        <v>489.67236467236467</v>
+      </c>
+      <c r="G8" s="20"/>
+      <c r="H8" s="31" t="e" vm="4">
+        <v>#VALUE!</v>
+      </c>
+      <c r="I8" s="36"/>
+      <c r="J8" s="36"/>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A9" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="B9" s="41">
+        <v>0.85</v>
+      </c>
+      <c r="C9" s="33"/>
+      <c r="E9" s="20" t="s">
+        <v>45</v>
+      </c>
+      <c r="F9" s="24">
+        <v>50</v>
+      </c>
+      <c r="G9" s="20"/>
+      <c r="H9" s="16" t="s">
+        <v>71</v>
+      </c>
+      <c r="J9" s="16" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A10" s="19" t="s">
+        <v>50</v>
+      </c>
+      <c r="B10" s="34">
+        <v>1500</v>
+      </c>
+      <c r="C10" s="33"/>
+      <c r="E10" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="F10" s="24">
+        <f>B10+F8/2</f>
+        <v>1744.8361823361824</v>
+      </c>
+      <c r="H10" s="20" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" ht="40.799999999999997" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="19" t="s">
+        <v>24</v>
+      </c>
+      <c r="B11" s="20">
+        <v>58</v>
+      </c>
+      <c r="C11" s="33"/>
+      <c r="E11" s="20" t="s">
+        <v>22</v>
+      </c>
+      <c r="F11" s="27">
+        <f>(1/(8*B4))*(F8/F9)*10000</f>
+        <v>20.926169430442936</v>
+      </c>
+      <c r="G11" s="39">
+        <v>22</v>
+      </c>
+      <c r="H11" s="31" t="e" vm="5">
+        <v>#VALUE!</v>
+      </c>
+      <c r="I11" s="36"/>
+      <c r="J11" s="36"/>
+      <c r="K11" s="37" t="s">
+        <v>53</v>
+      </c>
+      <c r="L11" s="37"/>
+    </row>
+    <row r="12" spans="1:13" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="19" t="s">
+        <v>30</v>
+      </c>
+      <c r="B12" s="20">
+        <v>50</v>
+      </c>
+      <c r="C12" s="33" t="s">
+        <v>44</v>
+      </c>
+      <c r="E12" s="20" t="s">
+        <v>22</v>
+      </c>
+      <c r="F12" s="27">
+        <f>(2*(B10*0.5))/(B4*(B2-B3))*100</f>
+        <v>23.310023310023308</v>
+      </c>
+      <c r="G12" s="39">
+        <v>23</v>
+      </c>
+      <c r="H12" s="31" t="e" vm="6">
+        <v>#VALUE!</v>
+      </c>
+      <c r="I12" s="36"/>
+      <c r="J12" s="36"/>
+      <c r="K12" s="37"/>
+      <c r="L12" s="37"/>
+      <c r="M12" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A13" s="19" t="s">
+        <v>61</v>
+      </c>
+      <c r="B13" s="20">
+        <v>6</v>
+      </c>
+      <c r="C13" s="21" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A14" s="19" t="s">
+        <v>66</v>
+      </c>
+      <c r="B14" s="20">
+        <v>97</v>
+      </c>
+      <c r="C14" s="21" t="s">
+        <v>62</v>
+      </c>
+      <c r="E14" s="20" t="s">
+        <v>56</v>
+      </c>
+      <c r="F14" s="24" t="s">
+        <v>58</v>
+      </c>
+      <c r="G14" s="20" t="s">
+        <v>60</v>
+      </c>
+      <c r="H14" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="K14" s="16" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" ht="33.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="E16" s="20" t="s">
+        <v>65</v>
+      </c>
+      <c r="F16" s="24">
+        <f>B13*F17*1000/(2*PI()*(B4/10)*G11*F17)</f>
+        <v>0.74198108667550278</v>
+      </c>
+      <c r="G16" s="20"/>
+      <c r="H16" s="31" t="e" vm="7">
+        <v>#VALUE!</v>
+      </c>
+      <c r="I16" s="30"/>
+      <c r="J16" s="30"/>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A17" s="19" t="s">
+        <v>37</v>
+      </c>
+      <c r="B17" s="20">
+        <f>2.4/1000</f>
+        <v>2.3999999999999998E-3</v>
+      </c>
+      <c r="C17" s="21" t="s">
+        <v>36</v>
+      </c>
+      <c r="E17" s="20" t="s">
+        <v>63</v>
+      </c>
+      <c r="F17" s="24">
+        <f>B3/B10*1000</f>
+        <v>3.3333333333333335</v>
+      </c>
+      <c r="G17" s="20"/>
+    </row>
+    <row r="18" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="19" t="s">
+        <v>40</v>
+      </c>
+      <c r="B18" s="24">
+        <v>40</v>
+      </c>
+      <c r="C18" s="21" t="s">
+        <v>41</v>
+      </c>
+      <c r="E18" s="20" t="s">
+        <v>69</v>
+      </c>
+      <c r="F18" s="24">
+        <f>B10/(2*PI()*B3*G11)*1000</f>
+        <v>2170.2946785258455</v>
+      </c>
+      <c r="G18" s="20"/>
+      <c r="H18" s="31" t="e" vm="8">
+        <v>#VALUE!</v>
+      </c>
+      <c r="I18" s="30"/>
+      <c r="J18" s="30"/>
+      <c r="K18" s="16" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A19" s="19" t="s">
+        <v>38</v>
+      </c>
+      <c r="B19" s="20">
+        <f>B18*B17</f>
+        <v>9.5999999999999988E-2</v>
+      </c>
+      <c r="C19" s="21" t="s">
+        <v>39</v>
+      </c>
+      <c r="E19" s="20" t="s">
+        <v>67</v>
+      </c>
+      <c r="F19" s="24">
+        <f>B4/10</f>
+        <v>58.5</v>
+      </c>
+      <c r="G19" s="20"/>
+      <c r="H19" s="16" t="s">
+        <v>42</v>
+      </c>
+      <c r="I19" s="16" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="E20" s="20" t="s">
+        <v>29</v>
+      </c>
+      <c r="F20" s="24">
+        <f>1/(2*PI()*SQRT(G3*G11))</f>
+        <v>9.7953096209561252</v>
+      </c>
+      <c r="G20" s="20"/>
+    </row>
+    <row r="21" spans="1:11" ht="28.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="E21" s="20" t="s">
+        <v>64</v>
+      </c>
+      <c r="F21" s="40">
+        <f>B3*1000/(F16*B6*B14)</f>
+        <v>86.839126829253942</v>
+      </c>
+      <c r="G21" s="42" t="s">
+        <v>73</v>
+      </c>
+      <c r="H21" s="31" t="e" vm="9">
+        <v>#VALUE!</v>
+      </c>
+      <c r="I21" s="30"/>
+    </row>
+    <row r="22" spans="1:11" ht="33" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="E22" s="20" t="s">
+        <v>77</v>
+      </c>
+      <c r="F22" s="40">
+        <f>G11*B11/(F21)</f>
+        <v>14.693837289600053</v>
+      </c>
+      <c r="G22" s="20"/>
+      <c r="H22" s="31" t="e" vm="10">
+        <v>#VALUE!</v>
+      </c>
+      <c r="I22" s="30"/>
+    </row>
+    <row r="23" spans="1:11" ht="32.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="E23" s="20" t="s">
+        <v>76</v>
+      </c>
+      <c r="F23" s="40">
+        <f>1000000000/(2*PI()*F21*F18)</f>
+        <v>844.47340744827898</v>
+      </c>
+      <c r="G23" s="20" t="s">
+        <v>74</v>
+      </c>
+      <c r="H23" s="31" t="e" vm="11">
+        <v>#VALUE!</v>
+      </c>
+      <c r="I23" s="30"/>
+    </row>
+    <row r="24" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="E24" s="20" t="s">
+        <v>33</v>
+      </c>
+      <c r="F24" s="24">
+        <f>F8/(2*SQRT(3))</f>
+        <v>141.35623577915518</v>
+      </c>
+      <c r="G24" s="20"/>
+    </row>
+    <row r="25" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="E25" s="20" t="s">
+        <v>34</v>
+      </c>
+      <c r="F25" s="28">
+        <v>2.5000000000000001E-3</v>
+      </c>
+      <c r="G25" s="20"/>
+    </row>
+  </sheetData>
+  <mergeCells count="13">
+    <mergeCell ref="H21:I21"/>
+    <mergeCell ref="H23:I23"/>
+    <mergeCell ref="H22:I22"/>
+    <mergeCell ref="H8:J8"/>
+    <mergeCell ref="H12:J12"/>
+    <mergeCell ref="K11:L12"/>
+    <mergeCell ref="H4:J4"/>
+    <mergeCell ref="H18:J18"/>
+    <mergeCell ref="H16:J16"/>
+    <mergeCell ref="E1:F1"/>
+    <mergeCell ref="H2:J2"/>
+    <mergeCell ref="H3:K3"/>
+    <mergeCell ref="H11:J11"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{39493502-BC7B-4038-881F-3492D7D21630}">
+  <dimension ref="A1:L20"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="24.5546875" style="16" customWidth="1"/>
+    <col min="2" max="2" width="9.88671875" style="16" customWidth="1"/>
+    <col min="3" max="3" width="22.5546875" style="16" customWidth="1"/>
+    <col min="4" max="4" width="8.88671875" style="16"/>
+    <col min="5" max="5" width="20.6640625" style="16" customWidth="1"/>
+    <col min="6" max="6" width="8.44140625" style="29" customWidth="1"/>
+    <col min="7" max="7" width="11.21875" style="16" customWidth="1"/>
+    <col min="8" max="8" width="12" style="16" customWidth="1"/>
+    <col min="9" max="12" width="8.88671875" style="16"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A1" s="15" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="15" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1" s="17" t="s">
+        <v>7</v>
+      </c>
+      <c r="F1" s="17"/>
+      <c r="G1" s="18" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" ht="43.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="19" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="34">
+        <v>36</v>
+      </c>
+      <c r="C2" s="33"/>
+      <c r="E2" s="22" t="s">
+        <v>3</v>
+      </c>
+      <c r="F2" s="23">
+        <f>206033/(B4^1.0888)</f>
+        <v>200.01265706102132</v>
+      </c>
+      <c r="G2" s="20"/>
+      <c r="H2" s="31" t="e" vm="1">
+        <v>#VALUE!</v>
+      </c>
+      <c r="I2" s="30"/>
+      <c r="J2" s="30"/>
+      <c r="K2" s="16" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" ht="37.200000000000003" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="19" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" s="34">
+        <v>16</v>
+      </c>
+      <c r="C3" s="33"/>
+      <c r="E3" s="20" t="s">
+        <v>52</v>
+      </c>
+      <c r="F3" s="25">
+        <f xml:space="preserve"> ((16-5)/(B5*B10))*(B3/(B2*B4))</f>
+        <v>1.8571277830537089E-5</v>
+      </c>
+      <c r="G3" s="20">
+        <f>20*10^-6</f>
+        <v>1.9999999999999998E-5</v>
+      </c>
+      <c r="H3" s="31" t="e" vm="2">
+        <v>#VALUE!</v>
+      </c>
+      <c r="I3" s="36"/>
+      <c r="J3" s="36"/>
+      <c r="K3" s="36"/>
+      <c r="L3" s="16" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" ht="29.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="19" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4" s="34">
+        <v>585</v>
+      </c>
+      <c r="C4" s="32" t="s">
+        <v>46</v>
+      </c>
+      <c r="E4" s="20" t="s">
+        <v>10</v>
+      </c>
+      <c r="F4" s="24">
+        <f>F5*(B3-0.8)/0.8</f>
+        <v>190</v>
+      </c>
+      <c r="G4" s="20">
+        <v>52.3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A5" s="19" t="s">
+        <v>48</v>
+      </c>
+      <c r="B5" s="33">
+        <v>0.3</v>
+      </c>
+      <c r="C5" s="35" t="s">
+        <v>49</v>
+      </c>
+      <c r="E5" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="F5" s="24">
+        <v>10</v>
+      </c>
+      <c r="G5" s="20"/>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A6" s="19" t="s">
+        <v>12</v>
+      </c>
+      <c r="B6" s="20">
+        <v>0.8</v>
+      </c>
+      <c r="C6" s="33"/>
+      <c r="E6" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="F6" s="24">
+        <f>(B8*B7)/(B6*0.8)</f>
+        <v>15.624999999999996</v>
+      </c>
+      <c r="G6" s="20"/>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A7" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="B7" s="20">
+        <v>2</v>
+      </c>
+      <c r="C7" s="33"/>
+      <c r="E7" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="F7" s="24">
+        <f>B3/(B2*B9)</f>
+        <v>0.52287581699346408</v>
+      </c>
+      <c r="G7" s="20"/>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A8" s="19" t="s">
+        <v>14</v>
+      </c>
+      <c r="B8" s="20">
+        <v>5</v>
+      </c>
+      <c r="C8" s="33"/>
+      <c r="E8" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="F8" s="24">
+        <f>(B2-B3)*F7/(B4*G3)</f>
+        <v>893.80481537344292</v>
+      </c>
+      <c r="G8" s="20"/>
+      <c r="H8" s="16" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A9" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="B9" s="26">
+        <v>0.85</v>
+      </c>
+      <c r="C9" s="33"/>
+      <c r="E9" s="20" t="s">
+        <v>45</v>
+      </c>
+      <c r="F9" s="24">
+        <f>F8*B11/1000</f>
+        <v>51.84067929165969</v>
+      </c>
+      <c r="G9" s="20"/>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A10" s="19" t="s">
+        <v>50</v>
+      </c>
+      <c r="B10" s="34">
+        <v>1500</v>
+      </c>
+      <c r="C10" s="33"/>
+      <c r="E10" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="F10" s="24">
+        <f>B10+F8/2</f>
+        <v>1946.9024076867215</v>
+      </c>
+      <c r="H10" s="20" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A11" s="19" t="s">
+        <v>24</v>
+      </c>
+      <c r="B11" s="20">
+        <v>58</v>
+      </c>
+      <c r="C11" s="33"/>
+      <c r="E11" s="20" t="s">
+        <v>22</v>
+      </c>
+      <c r="F11" s="27">
+        <f>((B2-F7)*F7)/(8*B4*F20)</f>
+        <v>1.5854812215186429</v>
+      </c>
+      <c r="G11" s="20">
+        <v>49</v>
+      </c>
+      <c r="H11" s="16">
+        <f>2*B10/(B4*F9)</f>
+        <v>9.8922413793103445E-2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A12" s="19" t="s">
+        <v>30</v>
+      </c>
+      <c r="B12" s="20">
+        <v>50</v>
+      </c>
+      <c r="C12" s="33" t="s">
+        <v>44</v>
+      </c>
+      <c r="E12" s="20" t="s">
+        <v>23</v>
+      </c>
+      <c r="F12" s="24">
+        <f>B3/B10*1000</f>
+        <v>10.666666666666666</v>
+      </c>
+      <c r="G12" s="20"/>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="E13" s="20" t="s">
+        <v>25</v>
+      </c>
+      <c r="F13" s="24">
+        <f>1/(2*PI()*G11*F12)*10^6</f>
+        <v>304.50563091561611</v>
+      </c>
+      <c r="G13" s="20"/>
+      <c r="H13" s="16" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="E14" s="20" t="s">
+        <v>35</v>
+      </c>
+      <c r="F14" s="24">
+        <f>B4*0.5</f>
+        <v>292.5</v>
+      </c>
+      <c r="G14" s="20"/>
+      <c r="H14" s="16" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="E15" s="20" t="s">
+        <v>29</v>
+      </c>
+      <c r="F15" s="24">
+        <f>1/(2*PI()*SQRT(G3*G11))</f>
+        <v>5.0840181672655502</v>
+      </c>
+      <c r="G15" s="20"/>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="E16" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="F16" s="24">
+        <v>15</v>
+      </c>
+      <c r="G16" s="20"/>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A17" s="19" t="s">
+        <v>37</v>
+      </c>
+      <c r="B17" s="20">
+        <f>2.4/1000</f>
+        <v>2.3999999999999998E-3</v>
+      </c>
+      <c r="C17" s="21" t="s">
+        <v>36</v>
+      </c>
+      <c r="E17" s="20" t="s">
+        <v>27</v>
+      </c>
+      <c r="F17" s="24">
+        <f>1/(2*PI()*F16*F15)*1000</f>
+        <v>2.0869967789998038</v>
+      </c>
+      <c r="G17" s="20"/>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A18" s="19" t="s">
+        <v>40</v>
+      </c>
+      <c r="B18" s="24">
+        <v>40</v>
+      </c>
+      <c r="C18" s="21" t="s">
+        <v>41</v>
+      </c>
+      <c r="E18" s="20" t="s">
+        <v>28</v>
+      </c>
+      <c r="F18" s="24">
+        <f>1/(2*PI()*F16*F14)*10^6</f>
+        <v>36.274630904135698</v>
+      </c>
+      <c r="G18" s="20"/>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A19" s="19" t="s">
+        <v>38</v>
+      </c>
+      <c r="B19" s="20">
+        <f>B18*B17</f>
+        <v>9.5999999999999988E-2</v>
+      </c>
+      <c r="C19" s="21" t="s">
+        <v>39</v>
+      </c>
+      <c r="E19" s="20" t="s">
+        <v>33</v>
+      </c>
+      <c r="F19" s="24">
+        <f>F8/(2*SQRT(3))</f>
+        <v>258.0192253794205</v>
+      </c>
+      <c r="G19" s="20"/>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="E20" s="20" t="s">
+        <v>34</v>
+      </c>
+      <c r="F20" s="28">
+        <v>2.5000000000000001E-3</v>
+      </c>
+      <c r="G20" s="20"/>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="E1:F1"/>
+    <mergeCell ref="H2:J2"/>
+    <mergeCell ref="H3:K3"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H19"/>
+  <dimension ref="A1:H20"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="24.5546875" customWidth="1"/>
@@ -758,15 +2132,13 @@
       </c>
       <c r="C9" s="4"/>
       <c r="E9" s="1" t="s">
-        <v>20</v>
+        <v>45</v>
       </c>
       <c r="F9" s="8">
-        <f>B9+F8/2</f>
-        <v>1788.0425674543321</v>
-      </c>
-      <c r="H9" s="1" t="s">
-        <v>21</v>
-      </c>
+        <f>F8*B10/1000</f>
+        <v>33.412937824702531</v>
+      </c>
+      <c r="G9" s="1"/>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
@@ -777,14 +2149,14 @@
       </c>
       <c r="C10" s="4"/>
       <c r="E10" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="F10" s="6">
-        <f>((B2-F6)*F6)/(8*B4*F19)</f>
-        <v>0.49121269925768196</v>
-      </c>
-      <c r="G10" s="1">
-        <v>49</v>
+        <v>20</v>
+      </c>
+      <c r="F10" s="8">
+        <f>B9+F8/2</f>
+        <v>1788.0425674543321</v>
+      </c>
+      <c r="H10" s="1" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.3">
@@ -798,66 +2170,72 @@
         <v>44</v>
       </c>
       <c r="E11" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="F11" s="6">
+        <f>((B2-F6)*F6)/(8*B4*F20)</f>
+        <v>0.49121269925768196</v>
+      </c>
+      <c r="G11" s="1">
+        <v>49</v>
+      </c>
+      <c r="H11">
+        <f>2*B9/(B4*F9)</f>
+        <v>0.15347962382445141</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="E12" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="F11" s="8">
+      <c r="F12" s="8">
         <f>B3/B9*1000</f>
         <v>3.3333333333333335</v>
       </c>
-      <c r="G11" s="1"/>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="E12" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="F12" s="8">
-        <f>1/(2*PI()*G10*F11)*10^6</f>
-        <v>974.41801892997148</v>
-      </c>
       <c r="G12" s="1"/>
-      <c r="H12" t="s">
-        <v>43</v>
-      </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.3">
       <c r="E13" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="F13" s="8">
+        <f>1/(2*PI()*G11*F12)*10^6</f>
+        <v>974.41801892997148</v>
+      </c>
+      <c r="G13" s="1"/>
+      <c r="H13" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="E14" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="F13" s="8">
+      <c r="F14" s="8">
         <f>B4*0.5</f>
         <v>292.5</v>
       </c>
-      <c r="G13" s="1"/>
-      <c r="H13" t="s">
+      <c r="G14" s="1"/>
+      <c r="H14" t="s">
         <v>42</v>
       </c>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="E14" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="F14" s="8">
-        <f>1/(2*PI()*SQRT(G7*G10))</f>
-        <v>6.5634392312118104</v>
-      </c>
-      <c r="G14" s="1"/>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.3">
       <c r="E15" s="1" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="F15" s="8">
-        <v>15</v>
+        <f>1/(2*PI()*SQRT(G7*G11))</f>
+        <v>6.5634392312118104</v>
       </c>
       <c r="G15" s="1"/>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.3">
       <c r="E16" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F16" s="8">
-        <f>1/(2*PI()*F15*F14)*1000</f>
-        <v>1.6165807537309522</v>
+        <v>15</v>
       </c>
       <c r="G16" s="1"/>
     </row>
@@ -873,11 +2251,11 @@
         <v>36</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F17" s="8">
-        <f>1/(2*PI()*F15*F13)*10^6</f>
-        <v>36.274630904135698</v>
+        <f>1/(2*PI()*F16*F15)*1000</f>
+        <v>1.6165807537309522</v>
       </c>
       <c r="G17" s="1"/>
     </row>
@@ -892,11 +2270,11 @@
         <v>41</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="F18" s="8">
-        <f>F8/(2*SQRT(3))</f>
-        <v>166.30145385782964</v>
+        <f>1/(2*PI()*F16*F14)*10^6</f>
+        <v>36.274630904135698</v>
       </c>
       <c r="G18" s="1"/>
     </row>
@@ -912,12 +2290,22 @@
         <v>39</v>
       </c>
       <c r="E19" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="F19" s="8">
+        <f>F8/(2*SQRT(3))</f>
+        <v>166.30145385782964</v>
+      </c>
+      <c r="G19" s="1"/>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="E20" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="F19" s="7">
+      <c r="F20" s="7">
         <v>2.5000000000000001E-3</v>
       </c>
-      <c r="G19" s="1"/>
+      <c r="G20" s="1"/>
     </row>
   </sheetData>
   <mergeCells count="1">
